--- a/output/pdf_financials_xlsx/CPAU.xlsx
+++ b/output/pdf_financials_xlsx/CPAU.xlsx
@@ -5886,49 +5886,49 @@
         <v>1.800638</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.248346</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.301661</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.470854</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.470854</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.470854</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.491261</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.64454</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.036924</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.246422</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.300079</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.166251</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>8.885301</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>10.355202</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>10.62524</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>10.752727</v>
       </c>
     </row>
     <row r="93">
@@ -10183,7 +10183,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -11044,7 +11048,11 @@
           <t>Share-based payments reserve 10</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11840,7 +11848,11 @@
           <t>Share-based payments reserve 11</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -12434,7 +12446,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -12919,7 +12935,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -13699,7 +13719,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CPAU.xlsx
+++ b/output/pdf_financials_xlsx/CPAU.xlsx
@@ -1029,16 +1029,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.033691</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.011143</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.012933</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001767</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1056,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.9e-05</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.00012</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>9.3e-05</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000104</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.007201</v>
       </c>
       <c r="R12" s="3" t="n">
         <v>0</v>
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.283751</v>
+        <v>-3.317442</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.386891</v>
+        <v>-1.398034</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.075632</v>
+        <v>-4.088565</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.795536</v>
+        <v>-0.797303</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.6483139999999999</v>
@@ -2002,10 +2002,10 @@
         <v>-0.36281</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.845423</v>
+        <v>-0.845442</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.710765</v>
+        <v>-0.710885</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-2.856287</v>
@@ -2014,13 +2014,13 @@
         <v>-1.350103</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.345089</v>
+        <v>-1.345182</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-2.597402</v>
+        <v>-2.597506</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-1.377115</v>
+        <v>-1.384316</v>
       </c>
       <c r="R27" s="3" t="n">
         <v>-10.06072</v>
@@ -2091,16 +2091,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.283751</v>
+        <v>-3.317442</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.386891</v>
+        <v>-1.398034</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.074879</v>
+        <v>-4.087812</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.791916</v>
+        <v>-0.793683</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.644477</v>
@@ -2118,10 +2118,10 @@
         <v>-0.36281</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.845423</v>
+        <v>-0.845442</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.710765</v>
+        <v>-0.710885</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-2.856287</v>
@@ -2130,13 +2130,13 @@
         <v>-1.350103</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.345089</v>
+        <v>-1.345182</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-2.597402</v>
+        <v>-2.597506</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.377115</v>
+        <v>-1.384316</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>-10.06072</v>
@@ -2410,43 +2410,43 @@
         <v>0.057208</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.10874</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.039984</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001411</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.05813</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.141168</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.001345</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.017582</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.004429</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>3.271584</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.674189</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.875072</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.004193</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.110403</v>
       </c>
     </row>
     <row r="35">
@@ -2526,43 +2526,43 @@
         <v>0.057208</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.10874</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.039984</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001411</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.05813</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.141168</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.001345</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.017582</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.004429</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>3.271584</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.674189</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.875072</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>2.37</v>
+        <v>2.374193</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0.33</v>
+        <v>0.440403</v>
       </c>
     </row>
     <row r="37">
@@ -3222,43 +3222,43 @@
         <v>0.030379</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.169553</v>
+        <v>0.060813</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.071925</v>
+        <v>0.031941</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.02555</v>
+        <v>0.024139</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08562400000000001</v>
+        <v>0.027494</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.160314</v>
+        <v>0.019146</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.032367</v>
+        <v>0.031022</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.07091699999999999</v>
+        <v>0.053335</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.059775</v>
+        <v>0.055346</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>3.769476</v>
+        <v>0.497892</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.136881</v>
+        <v>0.462692</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>2.138444</v>
+        <v>0.263372</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.189325</v>
+        <v>0.185132</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.286249</v>
+        <v>0.175846</v>
       </c>
     </row>
     <row r="49">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24914,7 +24914,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -25209,7 +25209,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -31764,7 +31764,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -34709,7 +34709,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" s="5" t="n">
